--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1512</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>99.47%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>62.05</v>
+        <v>79.34</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>178.72</v>
+        <v>186.32</v>
       </c>
     </row>
     <row r="9">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>13.6</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="10">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>28.54</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="11">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>35.77</v>
+        <v>31.25</v>
       </c>
     </row>
   </sheetData>

--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>79.34</v>
+        <v>182.12</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>186.32</v>
+        <v>195.55</v>
       </c>
     </row>
     <row r="9">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11.93</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="10">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>22.27</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="11">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>31.25</v>
+        <v>25.11</v>
       </c>
     </row>
   </sheetData>
